--- a/Model_Run_Tracking.xlsx
+++ b/Model_Run_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model objective analysis/quantity discount/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{5CFCC789-D81B-4930-8049-C9AA0660C86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80614ECB-48B0-4860-9106-A3BC935E48A9}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{5CFCC789-D81B-4930-8049-C9AA0660C86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68524C74-CB6F-46BA-85F7-87E38B77453F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F57EBA8E-41C8-44C1-B306-1EA5435EF83A}"/>
+    <workbookView xWindow="20370" yWindow="-2565" windowWidth="29040" windowHeight="15720" xr2:uid="{F57EBA8E-41C8-44C1-B306-1EA5435EF83A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Model</t>
   </si>
@@ -44,58 +44,22 @@
     <t>OBJ</t>
   </si>
   <si>
-    <t>UG</t>
-  </si>
-  <si>
     <t>Method/Enhancements</t>
   </si>
   <si>
-    <t>L-Shaped, Partial benders, SEC (F)</t>
-  </si>
-  <si>
-    <t>L-Shaped, Partial benders, Two-Phase, SEC (F)</t>
-  </si>
-  <si>
     <t>Termination Criteria</t>
   </si>
   <si>
     <t>Final Gap</t>
   </si>
   <si>
-    <t>Tolerance reached</t>
-  </si>
-  <si>
     <t>Time (hrs)</t>
   </si>
   <si>
-    <t>Max iterations (500)</t>
-  </si>
-  <si>
-    <t>Solution Stability (&gt;10 w/o change)</t>
-  </si>
-  <si>
     <t>Missed Doses Total</t>
   </si>
   <si>
-    <t>UG3</t>
-  </si>
-  <si>
-    <t>UG4</t>
-  </si>
-  <si>
-    <t>UG2P</t>
-  </si>
-  <si>
     <t>Trial</t>
-  </si>
-  <si>
-    <t>UG2P2</t>
-  </si>
-  <si>
-    <t>UG2</t>
-  </si>
-  <si>
-    <t>L-Shaped, Partial benders, SEC (F) (5x7)</t>
   </si>
 </sst>
 </file>
@@ -161,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -169,9 +133,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -187,10 +148,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -526,204 +483,92 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="G3" s="4">
-        <f>5030.5/60/60</f>
-        <v>1.3973611111111111</v>
-      </c>
-      <c r="H3" s="5">
-        <v>134805434.48155099</v>
-      </c>
-      <c r="I3" s="5">
-        <v>107653040.14479101</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.47870000000000001</v>
-      </c>
-      <c r="G4" s="4">
-        <f>33360/60/60</f>
-        <v>9.2666666666666675</v>
-      </c>
-      <c r="H4" s="5">
-        <v>131833957.000376</v>
-      </c>
-      <c r="I4" s="5">
-        <v>184260226.92799199</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.14580000000000001</v>
-      </c>
-      <c r="G5" s="7">
-        <v>44.75</v>
-      </c>
-      <c r="H5" s="8">
-        <v>77383821.392349899</v>
-      </c>
-      <c r="I5" s="8">
-        <v>149831231.39600301</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.95240000000000002</v>
-      </c>
-      <c r="G6" s="4">
-        <f>14794/60/60</f>
-        <v>4.1094444444444447</v>
-      </c>
-      <c r="H6" s="5">
-        <v>319884936.33695197</v>
-      </c>
-      <c r="I6" s="6">
-        <v>676201492.22444797</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.99060000000000004</v>
-      </c>
-      <c r="G7" s="4">
-        <f>11967/60/60</f>
-        <v>3.3241666666666663</v>
-      </c>
-      <c r="H7" s="5">
-        <v>546258958.41122794</v>
-      </c>
-      <c r="I7" s="6">
-        <v>908515323.25022995</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.88449999999999995</v>
-      </c>
-      <c r="G8" s="1">
-        <v>27.03</v>
-      </c>
-      <c r="H8" s="5">
-        <v>99671885.3749156</v>
-      </c>
-      <c r="I8" s="6">
-        <v>908515323.25022995</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
